--- a/XLibur.Tests/Resource/Examples/Ranges/CurrentRowColumn.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/CurrentRowColumn.xlsx
@@ -19,13 +19,13 @@
     <x:t>Red's Row:</x:t>
   </x:si>
   <x:si>
-    <x:t>Blue's Row:</x:t>
+    <x:t>B</x:t>
   </x:si>
   <x:si>
     <x:t>Red's Column:</x:t>
   </x:si>
   <x:si>
-    <x:t>B</x:t>
+    <x:t>Blue's Row:</x:t>
   </x:si>
   <x:si>
     <x:t>Green's Column:</x:t>
@@ -438,7 +438,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E1" s="1">
         <x:v>6</x:v>
@@ -449,13 +449,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">

--- a/XLibur.Tests/Resource/Examples/Ranges/CurrentRowColumn.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/CurrentRowColumn.xlsx
@@ -416,18 +416,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:E9"/>
-  <x:sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="13.853482" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="1.853482" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="9.140625" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="9.140625" style="1"/>
     <x:col min="4" max="4" width="15.710625" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="1.853482" style="1" customWidth="1"/>
-    <x:col min="6" max="16384" width="9.140625" style="1" customWidth="1"/>
+    <x:col min="6" max="16384" width="9.140625" style="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5">
@@ -476,10 +473,6 @@
       <x:c r="B9" s="4"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Ranges/CurrentRowColumn.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/CurrentRowColumn.xlsx
@@ -419,11 +419,11 @@
   <x:dimension ref="A1:E9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="13.853482" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="1.853482" style="1" customWidth="1"/>
+    <x:col min="1" max="1" width="13.424911" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="2.139196" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="9.140625" style="1"/>
-    <x:col min="4" max="4" width="15.710625" style="1" customWidth="1"/>
-    <x:col min="5" max="5" width="1.853482" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="15.282054" style="1" customWidth="1"/>
+    <x:col min="5" max="5" width="2.139196" style="1" customWidth="1"/>
     <x:col min="6" max="16384" width="9.140625" style="1"/>
   </x:cols>
   <x:sheetData>

--- a/XLibur.Tests/Resource/Examples/Ranges/CurrentRowColumn.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/CurrentRowColumn.xlsx
@@ -419,12 +419,12 @@
   <x:dimension ref="A1:E9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="13.424911" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="2.139196" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="9.140625" style="1"/>
-    <x:col min="4" max="4" width="15.282054" style="1" customWidth="1"/>
-    <x:col min="5" max="5" width="2.139196" style="1" customWidth="1"/>
-    <x:col min="6" max="16384" width="9.140625" style="1"/>
+    <x:col min="1" max="1" width="13.428571" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="2.142857" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="9.144286" style="1"/>
+    <x:col min="4" max="4" width="15.285714" style="1" customWidth="1"/>
+    <x:col min="5" max="5" width="2.142857" style="1" customWidth="1"/>
+    <x:col min="6" max="16384" width="9.144286" style="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:5">
